--- a/rev1/rev1 parts list.xlsx
+++ b/rev1/rev1 parts list.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5aa3693f9022e187/Desktop/Interactive-chessboard/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5aa3693f9022e187/Desktop/Interactive-chessboard/rev1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="152" documentId="11_F25DC773A252ABDACC1048B721DF46CE5ADE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1AC9F93C-6255-4C4A-BB2E-53C84F66717C}"/>
+  <xr:revisionPtr revIDLastSave="156" documentId="11_F25DC773A252ABDACC1048B721DF46CE5ADE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DA89DDA4-2934-47EB-9D2F-FB20504D165C}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -98,21 +98,12 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>https://www.digikey.ca/en/products/detail/vishay-dale-thin-film/PLT0805Z5001AST5/2120350</t>
-  </si>
-  <si>
-    <t>Power rating of 0.25W &lt;&lt; 3.3^2/5k = 0.002W</t>
-  </si>
-  <si>
     <t>150 ohm res</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.digikey.com/en/products/detail/yageo/RC0805FR-07150RL/727613 </t>
   </si>
   <si>
-    <t xml:space="preserve">To calculate desired resistance; we want 10mA of current, based on LED I-V characteristic, that is at 1.8V. R = (3.3-1.8)/0.01 = 150. Also, power rating of 0.125W &lt;&lt; 3.3^2/150 = 0.07W </t>
-  </si>
-  <si>
     <t xml:space="preserve">https://www.digikey.ca/en/products/detail/schurter-inc/1301-9314-24/8536705 </t>
   </si>
   <si>
@@ -132,6 +123,15 @@
   </si>
   <si>
     <t>May be too strong, but we can lift board off PCB. Should not be too weak</t>
+  </si>
+  <si>
+    <t>Power rating of 0.125W &gt;&gt; 3.3^2/5k = 0.002W</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To calculate desired resistance; we want 10mA of current, based on LED I-V characteristic, that is at 1.8V. R = (3.3-1.8)/0.01 = 150. Also, power rating of 0.125W &gt;&gt; 3.3^2/150 = 0.07W </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.digikey.ca/en/products/detail/vishay-dale/CRCW08055K00JNTA/5075662 </t>
   </si>
 </sst>
 </file>
@@ -204,6 +204,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -566,24 +570,24 @@
         <v>23</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="D8" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B9">
         <v>17</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D9" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
@@ -594,7 +598,7 @@
         <v>4</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
@@ -605,7 +609,7 @@
         <v>2</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
@@ -616,24 +620,24 @@
         <v>1</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D12" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B13">
         <v>16</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D13" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -644,12 +648,12 @@
     <hyperlink ref="C5" r:id="rId4" xr:uid="{7A80C98E-4DFF-4DC6-806C-25A5C06F2112}"/>
     <hyperlink ref="C6" r:id="rId5" xr:uid="{B9872BB7-81E6-4B5C-A406-C353CA7EAB32}"/>
     <hyperlink ref="C7" r:id="rId6" xr:uid="{44D8879D-8210-4387-A792-1C54938D138F}"/>
-    <hyperlink ref="C8" r:id="rId7" xr:uid="{5EECD905-F729-401B-A7B9-4215299C3DA2}"/>
-    <hyperlink ref="C9" r:id="rId8" xr:uid="{9DCFD59B-26A9-469E-872D-13852687B744}"/>
-    <hyperlink ref="C10" r:id="rId9" xr:uid="{3CBD9A6A-EF3D-41C3-ADEF-2CC72D3348C7}"/>
-    <hyperlink ref="C11" r:id="rId10" xr:uid="{C522B588-2350-4753-A1FD-07EC4FA19D1E}"/>
-    <hyperlink ref="C12" r:id="rId11" xr:uid="{C8419AF1-7C91-42FC-A1D5-E455FD04FEE1}"/>
-    <hyperlink ref="C13" r:id="rId12" xr:uid="{C0419577-EFDE-44BE-9EA1-095327913656}"/>
+    <hyperlink ref="C9" r:id="rId7" xr:uid="{9DCFD59B-26A9-469E-872D-13852687B744}"/>
+    <hyperlink ref="C10" r:id="rId8" xr:uid="{3CBD9A6A-EF3D-41C3-ADEF-2CC72D3348C7}"/>
+    <hyperlink ref="C11" r:id="rId9" xr:uid="{C522B588-2350-4753-A1FD-07EC4FA19D1E}"/>
+    <hyperlink ref="C12" r:id="rId10" xr:uid="{C8419AF1-7C91-42FC-A1D5-E455FD04FEE1}"/>
+    <hyperlink ref="C13" r:id="rId11" xr:uid="{C0419577-EFDE-44BE-9EA1-095327913656}"/>
+    <hyperlink ref="C8" r:id="rId12" xr:uid="{1484E6E2-90FE-41FD-91CD-99F24649BF1C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId13"/>
